--- a/src/main/resources/SheetJSFileUpload.xlsx
+++ b/src/main/resources/SheetJSFileUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-framework-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashwini\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BC0E2E-82E4-4224-AB65-331A56FBEA2C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E979CDDC-7803-4398-AA96-762CBF0AD513}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -32,9 +32,6 @@
     <t>Program Name</t>
   </si>
   <si>
-    <t>CFDA Data</t>
-  </si>
-  <si>
     <t>Organization</t>
   </si>
   <si>
@@ -44,9 +41,6 @@
     <t>Funded Amount</t>
   </si>
   <si>
-    <t>Start Date</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -65,9 +59,6 @@
     <t>ProgramName__c</t>
   </si>
   <si>
-    <t>CFDA_Data__c</t>
-  </si>
-  <si>
     <t>Account__c</t>
   </si>
   <si>
@@ -77,9 +68,6 @@
     <t>FundedAmount__c</t>
   </si>
   <si>
-    <t>StartDate__c</t>
-  </si>
-  <si>
     <t>Status__c</t>
   </si>
   <si>
@@ -92,9 +80,6 @@
     <t>STRING</t>
   </si>
   <si>
-    <t>BOOLEAN</t>
-  </si>
-  <si>
     <t>REFERENCE</t>
   </si>
   <si>
@@ -104,9 +89,6 @@
     <t>CURRENCY</t>
   </si>
   <si>
-    <t>DATE</t>
-  </si>
-  <si>
     <t>Program__c</t>
   </si>
   <si>
@@ -116,13 +98,10 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>0011C00001sjyB4QAI</t>
+  </si>
+  <si>
     <t>AutomationSheetJSUpload</t>
-  </si>
-  <si>
-    <t>0011C00001sjyB4QAI</t>
-  </si>
-  <si>
-    <t>Active</t>
   </si>
   <si>
     <t>AutomationSheetJSUploadForStatusAsBlank</t>
@@ -135,9 +114,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -169,7 +145,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,23 +485,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.8125" customWidth="1"/>
-    <col min="2" max="2" width="17.8125" customWidth="1"/>
-    <col min="3" max="3" width="37.3125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.8125" customWidth="1"/>
-    <col min="5" max="5" width="25.8125" customWidth="1"/>
-    <col min="6" max="6" width="28.8125" customWidth="1"/>
-    <col min="7" max="7" width="30.8125" customWidth="1"/>
-    <col min="8" max="8" width="27.8125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.8125" customWidth="1"/>
-    <col min="10" max="10" width="31.8125" customWidth="1"/>
-    <col min="11" max="11" width="26.8125" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="29.875" customWidth="1"/>
+    <col min="4" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="28.875" customWidth="1"/>
+    <col min="6" max="6" width="30.875" customWidth="1"/>
+    <col min="7" max="7" width="24.875" customWidth="1"/>
+    <col min="8" max="8" width="31.875" customWidth="1"/>
+    <col min="9" max="9" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -547,229 +521,184 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3">
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1">
         <v>5000</v>
       </c>
-      <c r="H3" s="1">
-        <v>43871</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4">
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1">
         <v>5000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.8125" customWidth="1"/>
-    <col min="2" max="2" width="17.8125" customWidth="1"/>
-    <col min="3" max="3" width="29.8125" customWidth="1"/>
-    <col min="4" max="4" width="27.8125" customWidth="1"/>
-    <col min="5" max="5" width="25.8125" customWidth="1"/>
-    <col min="6" max="6" width="28.8125" customWidth="1"/>
-    <col min="7" max="7" width="30.8125" customWidth="1"/>
-    <col min="8" max="8" width="27.8125" customWidth="1"/>
-    <col min="9" max="9" width="24.8125" customWidth="1"/>
-    <col min="10" max="10" width="31.8125" customWidth="1"/>
-    <col min="11" max="11" width="26.8125" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="29.875" customWidth="1"/>
+    <col min="4" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="28.875" customWidth="1"/>
+    <col min="6" max="6" width="30.875" customWidth="1"/>
+    <col min="7" max="7" width="24.875" customWidth="1"/>
+    <col min="8" max="8" width="31.875" customWidth="1"/>
+    <col min="9" max="9" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>18</v>
-      </c>
-      <c r="I1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A2" t="s">
-        <v>22</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -796,18 +725,12 @@
       </c>
       <c r="I5" t="s">
         <v>8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/SheetJSFileUpload.xlsx
+++ b/src/main/resources/SheetJSFileUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashwini\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workspace\govgrants-framework-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E979CDDC-7803-4398-AA96-762CBF0AD513}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F4F27D-3B27-4385-BF05-7A1AB73B5681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -108,6 +108,18 @@
   </si>
   <si>
     <t>AutomationSheetJSUploadForStatusAsBlank1</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Last Modified By</t>
+  </si>
+  <si>
+    <t>Created By</t>
+  </si>
+  <si>
+    <t>Actions</t>
   </si>
 </sst>
 </file>
@@ -143,8 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -486,82 +497,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.875" customWidth="1"/>
-    <col min="2" max="2" width="17.875" customWidth="1"/>
-    <col min="3" max="3" width="29.875" customWidth="1"/>
-    <col min="4" max="4" width="25.875" customWidth="1"/>
-    <col min="5" max="5" width="28.875" customWidth="1"/>
-    <col min="6" max="6" width="30.875" customWidth="1"/>
-    <col min="7" max="7" width="24.875" customWidth="1"/>
-    <col min="8" max="8" width="31.875" customWidth="1"/>
-    <col min="9" max="9" width="26.875" customWidth="1"/>
+    <col min="1" max="1" width="19.8984375" customWidth="1"/>
+    <col min="2" max="2" width="29.8984375" customWidth="1"/>
+    <col min="3" max="3" width="25.8984375" customWidth="1"/>
+    <col min="4" max="4" width="28.8984375" customWidth="1"/>
+    <col min="5" max="5" width="30.8984375" customWidth="1"/>
+    <col min="6" max="6" width="24.8984375" customWidth="1"/>
+    <col min="7" max="7" width="31.8984375" customWidth="1"/>
+    <col min="8" max="8" width="26.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="1" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1">
+      <c r="E3">
         <v>5000</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C4" s="1" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1">
+      <c r="E4">
         <v>5000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1 B1:C1 E1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -569,20 +579,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.875" customWidth="1"/>
-    <col min="2" max="2" width="17.875" customWidth="1"/>
-    <col min="3" max="3" width="29.875" customWidth="1"/>
-    <col min="4" max="4" width="25.875" customWidth="1"/>
-    <col min="5" max="5" width="28.875" customWidth="1"/>
-    <col min="6" max="6" width="30.875" customWidth="1"/>
-    <col min="7" max="7" width="24.875" customWidth="1"/>
-    <col min="8" max="8" width="31.875" customWidth="1"/>
-    <col min="9" max="9" width="26.875" customWidth="1"/>
+    <col min="1" max="1" width="19.8984375" customWidth="1"/>
+    <col min="2" max="2" width="17.8984375" customWidth="1"/>
+    <col min="3" max="3" width="29.8984375" customWidth="1"/>
+    <col min="4" max="4" width="25.8984375" customWidth="1"/>
+    <col min="5" max="5" width="28.8984375" customWidth="1"/>
+    <col min="6" max="6" width="30.8984375" customWidth="1"/>
+    <col min="7" max="7" width="24.8984375" customWidth="1"/>
+    <col min="8" max="8" width="31.8984375" customWidth="1"/>
+    <col min="9" max="9" width="26.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -611,7 +621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -640,7 +650,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -669,7 +679,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -698,7 +708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
